--- a/SPC26S1 - 02 February v2.xlsx
+++ b/SPC26S1 - 02 February v2.xlsx
@@ -1850,7 +1850,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
@@ -1883,10 +1883,10 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
-  </si>
-  <si>
-    <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down list, and anything not on the list is rejected so a typo cannot slip in. To add a new status, edit the list under Data &gt; Data Validation.</t>
+  </si>
+  <si>
+    <t>Statuses on the drop-down: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
   <si>
     <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
@@ -1916,7 +1916,7 @@
     <t>How this file feeds the master</t>
   </si>
   <si>
-    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds every claim for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>The link is matched on Primary Claim ID, not on row position, so sorting and filtering these sheets is safe. Do not edit that column, and do not rename the specialty sheet tabs.</t>
@@ -4611,8 +4611,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A9" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5991,8 +5991,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A11" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6856,8 +6856,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A6" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8259,8 +8259,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A11" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9106,8 +9106,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A6" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9135,8 +9135,9 @@
       <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>277</v>
+      <c r="A3" s="9" t="str">
+        <f>COUNTA(BH!$D$2:$D$1000,DME!$D$2:$D$1000,GAE!$D$2:$D$1000,ORTHO!$D$2:$D$1000,US!$D$2:$D$1000)&amp;" claims with a date of service in 2026-02 February, split into one sheet per specialty: BH, DME, GAE, ORTHO, US."</f>
+        <v>38 claims with a date of service in 2026-02 February, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -9158,28 +9159,33 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>281</v>
+      <c r="A8" s="9" t="str">
+        <f>"    1 - Due in 5 days or less: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;=0",BH!$L$2:$L$1000,"&lt;=5"),COUNTIFS(DME!$L$2:$L$1000,"&gt;=0",DME!$L$2:$L$1000,"&lt;=5"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;=0",GAE!$L$2:$L$1000,"&lt;=5"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;=0",ORTHO!$L$2:$L$1000,"&lt;=5"),COUNTIFS(US!$L$2:$L$1000,"&gt;=0",US!$L$2:$L$1000,"&lt;=5"))</f>
+        <v>    1 - Due in 5 days or less: 0</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>282</v>
+      <c r="A9" s="9" t="str">
+        <f>"    2 - Due in 6-30 days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;5",BH!$L$2:$L$1000,"&lt;=30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;5",DME!$L$2:$L$1000,"&lt;=30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;5",GAE!$L$2:$L$1000,"&lt;=30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;5",ORTHO!$L$2:$L$1000,"&lt;=30"),COUNTIFS(US!$L$2:$L$1000,"&gt;5",US!$L$2:$L$1000,"&lt;=30"))</f>
+        <v>    2 - Due in 6-30 days: 0</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>283</v>
+      <c r="A10" s="9" t="str">
+        <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
+        <v>    3 - Due in 31+ days: 18</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>284</v>
+      <c r="A11" s="9" t="str">
+        <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
+        <v>    4 - Past deadline: 17</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>285</v>
+      <c r="A12" s="9" t="str">
+        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <v>    5 - No limit on file: 3</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">

--- a/SPC26S1 - 02 February v2.xlsx
+++ b/SPC26S1 - 02 February v2.xlsx
@@ -2086,7 +2086,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="108">
+  <dxfs count="109">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3136,9 +3136,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFF9933"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3160,6 +3164,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4601,7 +4612,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -5981,7 +5995,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -6846,7 +6863,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -8249,7 +8269,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -9096,7 +9119,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -9120,7 +9146,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -9349,14 +9375,14 @@
     <row r="45" spans="1:1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Under Review - orange</t>
+          <t xml:space="preserve">    Under Review - bright orange, bold (follow up on these)</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Denied - red</t>
+          <t xml:space="preserve">    Denied, not worked yet (Latest Date Worked empty) - red</t>
         </is>
       </c>
     </row>
@@ -9377,6 +9403,13 @@
     <row r="49" spans="1:1">
       <c r="A49" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Denied, already worked (Latest Date Worked filled in) - light pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Any other status is left unshaded.</t>
         </is>
       </c>
@@ -9422,6 +9455,11 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="expression" dxfId="108" priority="9">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SPC26S1 - 02 February v2.xlsx
+++ b/SPC26S1 - 02 February v2.xlsx
@@ -1850,7 +1850,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically; Finalized claims with a Latest Date Worked have their deadline cells left empty and are not counted):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
@@ -3672,14 +3672,15 @@
         <v>-145</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($F2="","",$F2+90-TODAY()))</f>
         <v>-145</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>184</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,5,13))</f>
         <v>46155</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -3785,14 +3786,15 @@
         <v>-154</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+90-TODAY()))</f>
         <v>-154</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>163</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,5,4))</f>
         <v>46146</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -3896,14 +3898,15 @@
         <v>-148</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-148</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>213</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,5,10))</f>
         <v>46152</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -4007,14 +4010,15 @@
         <v>-144</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,5,14))</f>
         <v>46156</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -4118,14 +4122,15 @@
         <v>-140</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,5,18))</f>
         <v>46160</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -4231,14 +4236,15 @@
         <v>-139</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+90-TODAY()))</f>
         <v>-139</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>166</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,5,19))</f>
         <v>46161</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -4342,14 +4348,15 @@
         <v>-137</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,5,21))</f>
         <v>46163</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -4453,14 +4460,15 @@
         <v>-137</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,5,21))</f>
         <v>46163</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -4527,100 +4535,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L9">
-    <cfRule type="expression" dxfId="99" priority="1">
+    <cfRule type="expression" dxfId="99" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="2">
+    <cfRule type="expression" dxfId="98" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="3">
+    <cfRule type="expression" dxfId="97" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="4">
+    <cfRule type="expression" dxfId="96" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="5">
+    <cfRule type="expression" dxfId="95" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M9">
-    <cfRule type="expression" dxfId="94" priority="6">
+    <cfRule type="expression" dxfId="94" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="7">
+    <cfRule type="expression" dxfId="93" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="8">
+    <cfRule type="expression" dxfId="92" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="9">
+    <cfRule type="expression" dxfId="91" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="10">
+    <cfRule type="expression" dxfId="90" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N9">
-    <cfRule type="expression" dxfId="89" priority="11">
+    <cfRule type="expression" dxfId="89" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="12">
+    <cfRule type="expression" dxfId="88" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="13">
+    <cfRule type="expression" dxfId="87" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="14">
+    <cfRule type="expression" dxfId="86" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="15">
+    <cfRule type="expression" dxfId="85" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U9">
-    <cfRule type="expression" dxfId="84" priority="16">
+    <cfRule type="expression" dxfId="84" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="17">
+    <cfRule type="expression" dxfId="83" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="18">
+    <cfRule type="expression" dxfId="82" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="19">
+    <cfRule type="expression" dxfId="81" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="20">
+    <cfRule type="expression" dxfId="80" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4835,14 +4848,15 @@
         <v>141</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+120-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2027,2,23))</f>
         <v>46441</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -4950,14 +4964,15 @@
         <v>128</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>170</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+120-TODAY()))</f>
         <v>-75</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,2,10))</f>
         <v>46428</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -5065,14 +5080,15 @@
         <v>131</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>198</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>-47</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,2,13))</f>
         <v>46431</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -5184,14 +5200,15 @@
         <v>-141</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($F5="","",$F5+90-TODAY()))</f>
         <v>-141</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>292</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,5,17))</f>
         <v>46159</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -5297,14 +5314,15 @@
         <v>-138</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>-14</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>171</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,5,20))</f>
         <v>46162</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -5599,20 +5617,21 @@
       <c r="K9" s="3">
         <v>46300</v>
       </c>
-      <c r="L9" s="12">
+      <c t="str" r="L9" s="12">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v>128</v>
-      </c>
-      <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>198</v>
-      </c>
-      <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
-        <v>-47</v>
-      </c>
-      <c r="O9" s="6">
-        <v>46428</v>
+        <v/>
+      </c>
+      <c t="str" r="M9" s="12">
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N9" s="12">
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2027,2,10))</f>
+        <v/>
       </c>
       <c r="P9" s="5" t="s">
         <v>49</v>
@@ -5712,20 +5731,21 @@
       <c r="K10" s="3">
         <v>46246</v>
       </c>
-      <c r="L10" s="12">
+      <c t="str" r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>134</v>
-      </c>
-      <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>186</v>
-      </c>
-      <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
-        <v>-59</v>
-      </c>
-      <c r="O10" s="6">
-        <v>46434</v>
+        <v/>
+      </c>
+      <c t="str" r="M10" s="12">
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N10" s="12">
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2027,2,16))</f>
+        <v/>
       </c>
       <c r="P10" s="5" t="s">
         <v>49</v>
@@ -5829,20 +5849,21 @@
       <c r="K11" s="3">
         <v>46300</v>
       </c>
-      <c r="L11" s="12">
+      <c t="str" r="L11" s="12">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>136</v>
-      </c>
-      <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>166</v>
-      </c>
-      <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
-        <v>-79</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46436</v>
+        <v/>
+      </c>
+      <c t="str" r="M11" s="12">
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N11" s="12">
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2027,2,18))</f>
+        <v/>
       </c>
       <c r="P11" s="5" t="s">
         <v>49</v>
@@ -5910,100 +5931,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN11" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L11">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="2">
+    <cfRule type="expression" dxfId="78" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="3">
+    <cfRule type="expression" dxfId="77" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="4">
+    <cfRule type="expression" dxfId="76" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="5">
+    <cfRule type="expression" dxfId="75" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M11">
-    <cfRule type="expression" dxfId="74" priority="6">
+    <cfRule type="expression" dxfId="74" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="7">
+    <cfRule type="expression" dxfId="73" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="8">
+    <cfRule type="expression" dxfId="72" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="9">
+    <cfRule type="expression" dxfId="71" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="10">
+    <cfRule type="expression" dxfId="70" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N11">
-    <cfRule type="expression" dxfId="69" priority="11">
+    <cfRule type="expression" dxfId="69" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="12">
+    <cfRule type="expression" dxfId="68" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="13">
+    <cfRule type="expression" dxfId="67" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="14">
+    <cfRule type="expression" dxfId="66" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="15">
+    <cfRule type="expression" dxfId="65" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U11">
-    <cfRule type="expression" dxfId="64" priority="16">
+    <cfRule type="expression" dxfId="64" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="17">
+    <cfRule type="expression" dxfId="63" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="18">
+    <cfRule type="expression" dxfId="62" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="19">
+    <cfRule type="expression" dxfId="61" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="20">
+    <cfRule type="expression" dxfId="60" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6216,14 +6242,15 @@
         <v>120</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>200</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+120-TODAY()))</f>
         <v>-45</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2027,2,2))</f>
         <v>46420</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -6339,14 +6366,15 @@
         <v>120</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>35</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>220</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,2,2))</f>
         <v>46420</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -6460,14 +6488,15 @@
         <v>127</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>191</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>-54</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,2,9))</f>
         <v>46427</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -6575,14 +6604,15 @@
         <v>134</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>35</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>220</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,2,16))</f>
         <v>46434</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -6696,14 +6726,15 @@
         <v>-141</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+90-TODAY()))</f>
         <v>-141</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>219</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,5,17))</f>
         <v>46159</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -6778,100 +6809,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="59" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="2">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="3">
+    <cfRule type="expression" dxfId="57" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="4">
+    <cfRule type="expression" dxfId="56" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="55" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M6">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="54" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="7">
+    <cfRule type="expression" dxfId="53" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="8">
+    <cfRule type="expression" dxfId="52" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="9">
+    <cfRule type="expression" dxfId="51" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="10">
+    <cfRule type="expression" dxfId="50" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N6">
-    <cfRule type="expression" dxfId="49" priority="11">
+    <cfRule type="expression" dxfId="49" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="12">
+    <cfRule type="expression" dxfId="48" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="13">
+    <cfRule type="expression" dxfId="47" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="14">
+    <cfRule type="expression" dxfId="46" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="15">
+    <cfRule type="expression" dxfId="45" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U6">
-    <cfRule type="expression" dxfId="44" priority="16">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="17">
+    <cfRule type="expression" dxfId="43" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="18">
+    <cfRule type="expression" dxfId="42" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="19">
+    <cfRule type="expression" dxfId="41" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="20">
+    <cfRule type="expression" dxfId="40" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7084,14 +7120,15 @@
         <v>135</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>193</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+120-TODAY()))</f>
         <v>-52</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2027,2,17))</f>
         <v>46435</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -7197,14 +7234,15 @@
         <v>-131</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+90-TODAY()))</f>
         <v>-131</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>277</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,5,27))</f>
         <v>46169</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -7312,14 +7350,15 @@
         <v>138</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>156</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>-89</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,2,20))</f>
         <v>46438</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -7425,14 +7464,15 @@
         <v>144</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>267</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+120-TODAY()))</f>
         <v>22</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,2,26))</f>
         <v>46444</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -7546,14 +7586,15 @@
         <v>-151</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+90-TODAY()))</f>
         <v>-151</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+540-TODAY()))</f>
         <v>387</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,5,7))</f>
         <v>46149</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -7657,14 +7698,15 @@
         <v>-130</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>254</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>254</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,5,28))</f>
         <v>46170</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -7770,14 +7812,15 @@
         <v>-123</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+365-TODAY()))</f>
         <v>122</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+365-TODAY()))</f>
         <v>122</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,6,4))</f>
         <v>46177</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -7884,7 +7927,7 @@
       </c>
       <c r="M9" s="12"/>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+180-TODAY()))</f>
         <v>-13</v>
       </c>
       <c r="O9" s="6"/>
@@ -7980,20 +8023,21 @@
       <c r="K10" s="3">
         <v>46192</v>
       </c>
-      <c r="L10" s="12">
+      <c t="str" r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>-138</v>
-      </c>
-      <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
-        <v>113</v>
-      </c>
-      <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>298</v>
-      </c>
-      <c r="O10" s="6">
-        <v>46162</v>
+        <v/>
+      </c>
+      <c t="str" r="M10" s="12">
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N10" s="12">
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,5,20))</f>
+        <v/>
       </c>
       <c r="P10" s="5" t="s">
         <v>46</v>
@@ -8099,20 +8143,21 @@
       <c r="K11" s="3">
         <v>46195</v>
       </c>
-      <c r="L11" s="12">
+      <c t="str" r="L11" s="12">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>-152</v>
-      </c>
-      <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>207</v>
-      </c>
-      <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>207</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46148</v>
+        <v/>
+      </c>
+      <c t="str" r="M11" s="12">
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N11" s="12">
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,5,6))</f>
+        <v/>
       </c>
       <c r="P11" s="5" t="s">
         <v>46</v>
@@ -8184,100 +8229,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L11">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="3">
+    <cfRule type="expression" dxfId="37" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="36" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="5">
+    <cfRule type="expression" dxfId="35" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M11">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="34" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="7">
+    <cfRule type="expression" dxfId="33" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="8">
+    <cfRule type="expression" dxfId="32" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="31" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="10">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N11">
-    <cfRule type="expression" dxfId="29" priority="11">
+    <cfRule type="expression" dxfId="29" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="13">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="14">
+    <cfRule type="expression" dxfId="26" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="15">
+    <cfRule type="expression" dxfId="25" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U11">
-    <cfRule type="expression" dxfId="24" priority="16">
+    <cfRule type="expression" dxfId="24" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="23" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8494,14 +8544,15 @@
         <v>130</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+120-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2027,2,12))</f>
         <v>46430</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -8613,14 +8664,15 @@
         <v>122</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+120-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,2,4))</f>
         <v>46422</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -8732,14 +8784,15 @@
         <v>130</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>276</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>31</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,2,12))</f>
         <v>46430</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -8845,14 +8898,15 @@
         <v>135</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>275</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+120-TODAY()))</f>
         <v>30</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,2,17))</f>
         <v>46435</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -8958,14 +9012,15 @@
         <v>136</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>275</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+120-TODAY()))</f>
         <v>30</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2027,2,18))</f>
         <v>46436</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -9034,100 +9089,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN6" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M6">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N6">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="13">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U6">
-    <cfRule type="expression" dxfId="4" priority="16">
+    <cfRule type="expression" dxfId="4" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9199,18 +9259,18 @@
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="str">
         <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
-        <v>    3 - Due in 31+ days: 18</v>
+        <v>    3 - Due in 31+ days: 15</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
         <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
-        <v>    4 - Past deadline: 17</v>
+        <v>    4 - Past deadline: 15</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="str">
-        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <f>"    5 - No limit on file: "&amp;SUM(SUMPRODUCT((BH!$D$2:$D$1000&lt;&gt;"")*(BH!$L$2:$L$1000="")*(1-(TRIM(BH!$A$2:$A$1000)="Finalized")*(BH!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((DME!$D$2:$D$1000&lt;&gt;"")*(DME!$L$2:$L$1000="")*(1-(TRIM(DME!$A$2:$A$1000)="Finalized")*(DME!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((GAE!$D$2:$D$1000&lt;&gt;"")*(GAE!$L$2:$L$1000="")*(1-(TRIM(GAE!$A$2:$A$1000)="Finalized")*(GAE!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((ORTHO!$D$2:$D$1000&lt;&gt;"")*(ORTHO!$L$2:$L$1000="")*(1-(TRIM(ORTHO!$A$2:$A$1000)="Finalized")*(ORTHO!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((US!$D$2:$D$1000&lt;&gt;"")*(US!$L$2:$L$1000="")*(1-(TRIM(US!$A$2:$A$1000)="Finalized")*(US!$K$2:$K$1000&lt;&gt;""))))</f>
         <v>    5 - No limit on file: 3</v>
       </c>
     </row>
